--- a/artfynd/A 4059-2023 artfynd.xlsx
+++ b/artfynd/A 4059-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1328,6 +1328,137 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>82451218</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56159</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hässleholm-Lund, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>415091</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6222402</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Finja</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-07-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Brüsin, Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4059-2023 artfynd.xlsx
+++ b/artfynd/A 4059-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4059-2023 artfynd.xlsx
+++ b/artfynd/A 4059-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>82456719</v>
       </c>
       <c r="B2" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415090.8854908629</v>
+        <v>415091</v>
       </c>
       <c r="R2" t="n">
-        <v>6222401.732800992</v>
+        <v>6222402</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -806,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82449840</v>
+        <v>82456183</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415090.8854908629</v>
+        <v>415091</v>
       </c>
       <c r="R3" t="n">
-        <v>6222401.732800992</v>
+        <v>6222402</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -940,12 +930,7 @@
         <v>82455897</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415090.8854908629</v>
+        <v>415091</v>
       </c>
       <c r="R4" t="n">
-        <v>6222401.732800992</v>
+        <v>6222402</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1068,15 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82456183</v>
+        <v>82449840</v>
       </c>
       <c r="B5" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,26 +1064,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1127,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415090.8854908629</v>
+        <v>415091</v>
       </c>
       <c r="R5" t="n">
-        <v>6222401.732800992</v>
+        <v>6222402</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1202,12 +1182,7 @@
         <v>82451218</v>
       </c>
       <c r="B6" t="n">
-        <v>56188</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4059-2023 artfynd.xlsx
+++ b/artfynd/A 4059-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82456719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82456183</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82455897</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82449840</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,8 +1327,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82451218</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>